--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="分公司会员沉淀" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="未匹配门店" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="各分公司末位门店" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,14 +471,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23242</v>
+        <v>22262</v>
       </c>
       <c r="C3" t="n">
-        <v>23241</v>
+        <v>22261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+23242</t>
+          <t>+22262</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -489,14 +490,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42367</v>
+        <v>42063</v>
       </c>
       <c r="C4" t="n">
-        <v>42363</v>
+        <v>42060</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+42367</t>
+          <t>+42063</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -527,14 +528,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13186</v>
+        <v>12697</v>
       </c>
       <c r="C6" t="n">
-        <v>13186</v>
+        <v>12697</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+13186</t>
+          <t>+12697</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -561,18 +562,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>（未匹配门店）</t>
+          <t>未消费会员</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>408</v>
+        <v>11985</v>
       </c>
       <c r="C8" t="n">
-        <v>408</v>
+        <v>11871</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+408</t>
+          <t>+11985</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -580,36 +581,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>（无门店信息）</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11985</v>
+        <v>185368</v>
       </c>
       <c r="C9" t="n">
-        <v>11871</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+11985</t>
-        </is>
-      </c>
+        <v>185179</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>187549</v>
-      </c>
-      <c r="C10" t="n">
-        <v>187359</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -622,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,34 +619,580 @@
         </is>
       </c>
     </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>分公司</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>门店</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>会员数</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>APR北京长楹天街ASP</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>231</v>
+          <t>上海爱飞</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DJI上海天荟广场授权体验店</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>52</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>APR上海天空之城ASP</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>113</v>
+          <t>上海爱飞</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>299</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>APR上海前湾印象城ASP</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>64</v>
+          <t>上海爱飞</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DJI上海第一八佰伴授权体验店</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>339</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>上海爱飞</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DJI上海百联南桥购物中心授权体验店</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>366</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>上海爱飞</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DJI上海维璟印象城授权体验店</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>445</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>北京中恒</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>APR上海唐镇印象汇</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>54</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>北京中恒</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>APR上海三林印象汇</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>104</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>北京中恒</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>华为北京常营龙湖</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>111</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>北京中恒</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>APR北京昌发展万科</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>153</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>北京中恒</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>APR北京槐房万达</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>173</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>华为北京丰管路用户中心</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>华为北京回龙观一店</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>237</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>华为北京京投小站</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>246</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>华为北京上德银泰</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>327</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>华为北京丰台鑫嘉汇</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>348</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DJI北京龙湖长安天街授权体验店</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>115</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>DJI北京龙湖熙悦天街授权体验店</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>174</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DJI北京北投新奥天虹授权体验店</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>181</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DJI北京万柳华联授权体验店</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>280</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DJI北京首都机场授权体验店</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>351</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>四川新跃内购店</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>APR昆明万象城</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>33</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>APR成都武侯大悦城</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>35</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>APR成都天府大悦城</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>98</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>APR成都凯德魅力城</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>118</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>华为厦门思明星河COCO Park</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>11</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>华为厦门湖里江头</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>144</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>华为福州福清高山</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>145</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>华为厦门思明大西洋天虹</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>164</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>华为厦门思明君尚天虹</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>183</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,17 +452,19 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>20479</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20442</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+62</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>20417</v>
       </c>
-      <c r="C2" t="n">
-        <v>20380</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+20417</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -471,17 +473,19 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>22422</v>
+      </c>
+      <c r="C3" t="n">
+        <v>22421</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+160</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>22262</v>
       </c>
-      <c r="C3" t="n">
-        <v>22261</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+22262</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -490,17 +494,19 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>42154</v>
+      </c>
+      <c r="C4" t="n">
+        <v>42151</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+91</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>42063</v>
       </c>
-      <c r="C4" t="n">
-        <v>42060</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+42063</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -509,17 +515,19 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>61760</v>
+      </c>
+      <c r="C5" t="n">
+        <v>61726</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+123</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>61637</v>
       </c>
-      <c r="C5" t="n">
-        <v>61603</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+61637</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -528,17 +536,19 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>12758</v>
+      </c>
+      <c r="C6" t="n">
+        <v>12758</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+61</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>12697</v>
       </c>
-      <c r="C6" t="n">
-        <v>12697</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+12697</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -547,17 +557,19 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>14353</v>
+      </c>
+      <c r="C7" t="n">
+        <v>14353</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+46</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>14307</v>
       </c>
-      <c r="C7" t="n">
-        <v>14307</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+14307</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -566,17 +578,19 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>11983</v>
+      </c>
+      <c r="C8" t="n">
+        <v>11868</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>11985</v>
       </c>
-      <c r="C8" t="n">
-        <v>11871</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+11985</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -585,10 +599,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>185368</v>
+        <v>185909</v>
       </c>
       <c r="C9" t="n">
-        <v>185179</v>
+        <v>185719</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -667,7 +681,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -685,7 +699,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -703,7 +717,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -721,7 +735,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -739,7 +753,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -829,7 +843,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -901,7 +915,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -919,7 +933,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -937,7 +951,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -955,7 +969,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -991,7 +1005,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1009,7 +1023,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1041,11 +1055,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>APR昆明万象城</t>
+          <t>APR成都武侯大悦城</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1059,11 +1073,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>APR成都武侯大悦城</t>
+          <t>APR昆明万象城</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>20675</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20638</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+196</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>20479</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20442</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+62</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>20417</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>22970</v>
+      </c>
+      <c r="C3" t="n">
+        <v>22969</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+548</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>22422</v>
-      </c>
-      <c r="C3" t="n">
-        <v>22421</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+160</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>22262</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>42547</v>
+      </c>
+      <c r="C4" t="n">
+        <v>42544</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+393</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>42154</v>
-      </c>
-      <c r="C4" t="n">
-        <v>42151</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+91</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>42063</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>62317</v>
+      </c>
+      <c r="C5" t="n">
+        <v>62282</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+557</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>61760</v>
-      </c>
-      <c r="C5" t="n">
-        <v>61726</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+123</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>61637</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>12957</v>
+      </c>
+      <c r="C6" t="n">
+        <v>12957</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+199</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>12758</v>
-      </c>
-      <c r="C6" t="n">
-        <v>12758</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+61</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>12697</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>14491</v>
+      </c>
+      <c r="C7" t="n">
+        <v>14491</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+138</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>14353</v>
-      </c>
-      <c r="C7" t="n">
-        <v>14353</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+46</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>14307</v>
       </c>
     </row>
     <row r="8">
@@ -578,18 +578,18 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>12054</v>
+      </c>
+      <c r="C8" t="n">
+        <v>11938</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+71</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>11983</v>
-      </c>
-      <c r="C8" t="n">
-        <v>11868</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>11985</v>
       </c>
     </row>
     <row r="9">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>185909</v>
+        <v>188011</v>
       </c>
       <c r="C9" t="n">
-        <v>185719</v>
+        <v>187819</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -965,11 +965,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DJI北京龙湖熙悦天街授权体验店</t>
+          <t>DJI北京北投新奥天虹授权体验店</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -983,11 +983,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DJI北京北投新奥天虹授权体验店</t>
+          <t>DJI北京龙湖熙悦天街授权体验店</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D30" t="n">
         <v>4</v>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>20835</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20798</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+160</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>20675</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20638</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+196</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>20479</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>23530</v>
+      </c>
+      <c r="C3" t="n">
+        <v>23529</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+560</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>22970</v>
-      </c>
-      <c r="C3" t="n">
-        <v>22969</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+548</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>22422</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>42952</v>
+      </c>
+      <c r="C4" t="n">
+        <v>42949</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+405</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>42547</v>
-      </c>
-      <c r="C4" t="n">
-        <v>42544</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+393</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>42154</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>62795</v>
+      </c>
+      <c r="C5" t="n">
+        <v>62760</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+478</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>62317</v>
-      </c>
-      <c r="C5" t="n">
-        <v>62282</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+557</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>61760</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>13137</v>
+      </c>
+      <c r="C6" t="n">
+        <v>13137</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+180</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>12957</v>
-      </c>
-      <c r="C6" t="n">
-        <v>12957</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+199</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>12758</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>14633</v>
+      </c>
+      <c r="C7" t="n">
+        <v>14633</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+142</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>14491</v>
-      </c>
-      <c r="C7" t="n">
-        <v>14491</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+138</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>14353</v>
       </c>
     </row>
     <row r="8">
@@ -578,18 +578,18 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>12109</v>
+      </c>
+      <c r="C8" t="n">
+        <v>11993</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+55</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>12054</v>
-      </c>
-      <c r="C8" t="n">
-        <v>11938</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+71</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>11983</v>
       </c>
     </row>
     <row r="9">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>188011</v>
+        <v>189991</v>
       </c>
       <c r="C9" t="n">
-        <v>187819</v>
+        <v>189799</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -494,14 +494,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42952</v>
+        <v>42950</v>
       </c>
       <c r="C4" t="n">
-        <v>42949</v>
+        <v>42947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+405</t>
+          <t>+403</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -536,14 +536,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13137</v>
+        <v>13136</v>
       </c>
       <c r="C6" t="n">
-        <v>13137</v>
+        <v>13136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+180</t>
+          <t>+179</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>189991</v>
+        <v>189988</v>
       </c>
       <c r="C9" t="n">
-        <v>189799</v>
+        <v>189796</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -857,11 +857,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>华为北京丰管路用户中心</t>
+          <t>华为北京回龙观一店</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>240</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -875,11 +875,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>华为北京回龙观一店</t>
+          <t>华为北京京投小站</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -893,11 +893,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>华为北京京投小站</t>
+          <t>华为北京上德银泰</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>252</v>
+        <v>333</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -911,11 +911,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>华为北京上德银泰</t>
+          <t>华为北京丰台鑫嘉汇</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -929,11 +929,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>华为北京丰台鑫嘉汇</t>
+          <t>华为北京同成街华联</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -1037,11 +1037,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>四川新跃内购店</t>
+          <t>APR成都武侯大悦城</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1055,11 +1055,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>APR成都武侯大悦城</t>
+          <t>APR昆明万象城</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1073,11 +1073,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>APR昆明万象城</t>
+          <t>APR成都天府大悦城</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1091,11 +1091,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>APR成都天府大悦城</t>
+          <t>APR成都凯德魅力城</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1109,11 +1109,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>APR成都凯德魅力城</t>
+          <t>APR成都高新伊藤</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>118</v>
+        <v>171</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>20940</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20903</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+105</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>20835</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20798</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+160</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>20675</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>23910</v>
+      </c>
+      <c r="C3" t="n">
+        <v>23909</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+380</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>23530</v>
-      </c>
-      <c r="C3" t="n">
-        <v>23529</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+560</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>22970</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>43194</v>
+      </c>
+      <c r="C4" t="n">
+        <v>43191</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+244</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>42950</v>
-      </c>
-      <c r="C4" t="n">
-        <v>42947</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+403</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>42547</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>63104</v>
+      </c>
+      <c r="C5" t="n">
+        <v>63069</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+309</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>62795</v>
-      </c>
-      <c r="C5" t="n">
-        <v>62760</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+478</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>62317</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>13264</v>
+      </c>
+      <c r="C6" t="n">
+        <v>13264</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+128</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>13136</v>
-      </c>
-      <c r="C6" t="n">
-        <v>13136</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+179</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>12957</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>14709</v>
+      </c>
+      <c r="C7" t="n">
+        <v>14709</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+76</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>14633</v>
-      </c>
-      <c r="C7" t="n">
-        <v>14633</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+142</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>14491</v>
       </c>
     </row>
     <row r="8">
@@ -578,18 +578,18 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>12146</v>
+      </c>
+      <c r="C8" t="n">
+        <v>12029</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+37</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>12109</v>
-      </c>
-      <c r="C8" t="n">
-        <v>11993</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+55</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>12054</v>
       </c>
     </row>
     <row r="9">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>189988</v>
+        <v>191267</v>
       </c>
       <c r="C9" t="n">
-        <v>189796</v>
+        <v>191074</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -839,11 +839,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>APR北京槐房万达</t>
+          <t>APR北京北苑龙湖</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -911,11 +911,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>华为北京丰台鑫嘉汇</t>
+          <t>华为北京同成街华联</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -929,11 +929,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>华为北京同成街华联</t>
+          <t>华为北京丰台鑫嘉汇</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,38 +448,164 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>未消费会员</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>196130</v>
+        <v>21220</v>
       </c>
       <c r="C2" t="n">
-        <v>193234</v>
+        <v>21183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+183984</t>
+          <t>+280</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12146</v>
+        <v>20940</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>北京中恒</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>24819</v>
+      </c>
+      <c r="C3" t="n">
+        <v>24818</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+909</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>23910</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>43836</v>
+      </c>
+      <c r="C4" t="n">
+        <v>43833</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+642</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>43194</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>63817</v>
+      </c>
+      <c r="C5" t="n">
+        <v>63782</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+713</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>63104</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>13679</v>
+      </c>
+      <c r="C6" t="n">
+        <v>13679</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+415</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>13264</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>14948</v>
+      </c>
+      <c r="C7" t="n">
+        <v>14948</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+239</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>14709</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>未消费会员</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>12309</v>
+      </c>
+      <c r="C8" t="n">
+        <v>12177</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+163</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>12146</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>196130</v>
-      </c>
-      <c r="C3" t="n">
-        <v>193234</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>194628</v>
+      </c>
+      <c r="C9" t="n">
+        <v>194420</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -518,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,6 +669,546 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>上海爱飞</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DJI上海天荟广场授权体验店</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>89</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>上海爱飞</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>335</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>上海爱飞</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DJI上海第一八佰伴授权体验店</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>395</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>上海爱飞</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DJI上海百联南桥购物中心授权体验店</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>396</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>上海爱飞</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DJI上海维璟印象城授权体验店</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>481</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>北京中恒</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>APR上海唐镇印象汇</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>59</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>北京中恒</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>APR上海三林印象汇</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>111</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>北京中恒</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>华为北京常营龙湖</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>111</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>北京中恒</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>APR北京昌发展万科</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>175</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>北京中恒</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>APR北京北苑龙湖</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>200</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>华为北京回龙观一店</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>243</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>华为北京京投小站</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>258</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>华为北京上德银泰</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>338</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>华为北京同成街华联</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>367</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>华为北京丰台鑫嘉汇</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>391</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DJI北京龙湖长安天街授权体验店</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>184</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>DJI北京北投新奥天虹授权体验店</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>192</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DJI北京龙湖熙悦天街授权体验店</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>254</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DJI北京万柳华联授权体验店</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>307</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DJI北京首都机场授权体验店</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>382</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>APR昆明万象城</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>49</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>APR成都武侯大悦城</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>62</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>APR成都天府大悦城</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>119</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>APR成都凯德魅力城</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>120</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>APR成都双楠伊藤</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>187</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>华为厦门思明星河COCO Park</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>14</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>华为厦门湖里江头</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>144</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>华为福州福清高山</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>145</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>华为厦门思明大西洋天虹</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>167</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>华为厦门思明君尚天虹</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>191</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>21255</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21218</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+35</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>21220</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21183</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+280</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>20940</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>24925</v>
+      </c>
+      <c r="C3" t="n">
+        <v>24924</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+106</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>24819</v>
-      </c>
-      <c r="C3" t="n">
-        <v>24818</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+909</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>23910</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>43940</v>
+      </c>
+      <c r="C4" t="n">
+        <v>43937</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+104</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>43836</v>
-      </c>
-      <c r="C4" t="n">
-        <v>43833</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+642</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>43194</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>63924</v>
+      </c>
+      <c r="C5" t="n">
+        <v>63889</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+107</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>63817</v>
-      </c>
-      <c r="C5" t="n">
-        <v>63782</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+713</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>63104</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>13745</v>
+      </c>
+      <c r="C6" t="n">
+        <v>13745</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+66</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>13679</v>
-      </c>
-      <c r="C6" t="n">
-        <v>13679</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+415</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>13264</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>14991</v>
+      </c>
+      <c r="C7" t="n">
+        <v>14991</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+43</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>14948</v>
-      </c>
-      <c r="C7" t="n">
-        <v>14948</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+239</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>14709</v>
       </c>
     </row>
     <row r="8">
@@ -578,18 +578,18 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>12297</v>
+      </c>
+      <c r="C8" t="n">
+        <v>12164</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>12309</v>
-      </c>
-      <c r="C8" t="n">
-        <v>12177</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+163</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>12146</v>
       </c>
     </row>
     <row r="9">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>194628</v>
+        <v>195077</v>
       </c>
       <c r="C9" t="n">
-        <v>194420</v>
+        <v>194868</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1073,11 +1073,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>APR成都天府大悦城</t>
+          <t>APR成都凯德魅力城</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1091,11 +1091,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>APR成都凯德魅力城</t>
+          <t>APR成都天府大悦城</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>21360</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21323</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+105</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>21255</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21218</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+35</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>21220</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>25212</v>
+      </c>
+      <c r="C3" t="n">
+        <v>25211</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+287</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>24925</v>
-      </c>
-      <c r="C3" t="n">
-        <v>24924</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+106</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>24819</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>44249</v>
+      </c>
+      <c r="C4" t="n">
+        <v>44246</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+309</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>43940</v>
-      </c>
-      <c r="C4" t="n">
-        <v>43937</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+104</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>43836</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>64178</v>
+      </c>
+      <c r="C5" t="n">
+        <v>64142</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+254</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>63924</v>
-      </c>
-      <c r="C5" t="n">
-        <v>63889</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+107</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>63817</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>13861</v>
+      </c>
+      <c r="C6" t="n">
+        <v>13861</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+116</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>13745</v>
-      </c>
-      <c r="C6" t="n">
-        <v>13745</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+66</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>13679</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>15091</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15091</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+100</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>14991</v>
-      </c>
-      <c r="C7" t="n">
-        <v>14991</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+43</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>14948</v>
       </c>
     </row>
     <row r="8">
@@ -578,18 +578,18 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>12317</v>
+      </c>
+      <c r="C8" t="n">
+        <v>12184</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>12297</v>
-      </c>
-      <c r="C8" t="n">
-        <v>12164</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>-12</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>12309</v>
       </c>
     </row>
     <row r="9">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>195077</v>
+        <v>196268</v>
       </c>
       <c r="C9" t="n">
-        <v>194868</v>
+        <v>196058</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -713,11 +713,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DJI上海第一八佰伴授权体验店</t>
+          <t>DJI上海百联南桥购物中心授权体验店</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -731,11 +731,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DJI上海百联南桥购物中心授权体验店</t>
+          <t>DJI上海第一八佰伴授权体验店</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -947,11 +947,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DJI北京龙湖长安天街授权体验店</t>
+          <t>DJI北京北投新奥天虹授权体验店</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -965,11 +965,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DJI北京北投新奥天虹授权体验店</t>
+          <t>DJI北京龙湖长安天街授权体验店</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D30" t="n">
         <v>4</v>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>21534</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21497</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+174</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>21360</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21323</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+105</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>21255</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>25676</v>
+      </c>
+      <c r="C3" t="n">
+        <v>25675</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+464</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>25212</v>
-      </c>
-      <c r="C3" t="n">
-        <v>25211</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+287</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>24925</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>44869</v>
+      </c>
+      <c r="C4" t="n">
+        <v>44866</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+620</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>44249</v>
-      </c>
-      <c r="C4" t="n">
-        <v>44246</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+309</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>43940</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>64628</v>
+      </c>
+      <c r="C5" t="n">
+        <v>64592</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+450</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>64178</v>
-      </c>
-      <c r="C5" t="n">
-        <v>64142</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+254</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>63924</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>14006</v>
+      </c>
+      <c r="C6" t="n">
+        <v>14006</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+145</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>13861</v>
-      </c>
-      <c r="C6" t="n">
-        <v>13861</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+116</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>13745</v>
       </c>
     </row>
     <row r="7">
@@ -557,55 +557,74 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>15229</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15229</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+138</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>15091</v>
-      </c>
-      <c r="C7" t="n">
-        <v>15091</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+100</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>14991</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>未消费会员</t>
+          <t>（未匹配门店）</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12317</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>12184</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+20</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>12297</v>
-      </c>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>未消费会员</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>12359</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12225</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+42</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>12317</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>196268</v>
-      </c>
-      <c r="C9" t="n">
-        <v>196058</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>198302</v>
+      </c>
+      <c r="C10" t="n">
+        <v>198091</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -618,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,6 +650,16 @@
         <is>
           <t>记录数</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DJI上海FFC滨江悅里授权体验店</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +710,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -699,7 +728,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -717,7 +746,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -735,7 +764,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -753,7 +782,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -825,7 +854,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -843,7 +872,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -861,7 +890,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -879,7 +908,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -897,7 +926,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -933,7 +962,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -951,7 +980,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -969,7 +998,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -987,7 +1016,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1023,7 +1052,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1059,7 +1088,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1077,7 +1106,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1095,7 +1124,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1113,7 +1142,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1131,7 +1160,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1185,7 +1214,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D30" t="n">
         <v>4</v>
@@ -1203,7 +1232,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>21692</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21655</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+158</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>21534</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21497</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+174</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>21360</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>26095</v>
+      </c>
+      <c r="C3" t="n">
+        <v>26094</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+419</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>25676</v>
-      </c>
-      <c r="C3" t="n">
-        <v>25675</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+464</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>25212</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>45408</v>
+      </c>
+      <c r="C4" t="n">
+        <v>45405</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+539</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>44869</v>
-      </c>
-      <c r="C4" t="n">
-        <v>44866</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+620</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>44249</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>64956</v>
+      </c>
+      <c r="C5" t="n">
+        <v>64920</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+328</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>64628</v>
-      </c>
-      <c r="C5" t="n">
-        <v>64592</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+450</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>64178</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>14165</v>
+      </c>
+      <c r="C6" t="n">
+        <v>14165</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+159</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>14006</v>
-      </c>
-      <c r="C6" t="n">
-        <v>14006</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+145</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>13861</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>15397</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15397</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+168</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>15229</v>
-      </c>
-      <c r="C7" t="n">
-        <v>15229</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+138</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>15091</v>
       </c>
     </row>
     <row r="8">
@@ -583,12 +583,12 @@
       <c r="C8" t="n">
         <v>1</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -597,18 +597,18 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>12382</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12248</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+23</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>12359</v>
-      </c>
-      <c r="C9" t="n">
-        <v>12225</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+42</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>12317</v>
       </c>
     </row>
     <row r="10">
@@ -618,10 +618,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>198302</v>
+        <v>200096</v>
       </c>
       <c r="C10" t="n">
-        <v>198091</v>
+        <v>199885</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21692</v>
+        <v>21870</v>
       </c>
       <c r="C2" t="n">
-        <v>21655</v>
+        <v>21832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+158</t>
+          <t>+94</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>21534</v>
+        <v>21776</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26095</v>
+        <v>26691</v>
       </c>
       <c r="C3" t="n">
-        <v>26094</v>
+        <v>26690</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+419</t>
+          <t>+301</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25676</v>
+        <v>26390</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45408</v>
+        <v>46088</v>
       </c>
       <c r="C4" t="n">
-        <v>45405</v>
+        <v>46085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+539</t>
+          <t>+323</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44869</v>
+        <v>45765</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64956</v>
+        <v>65426</v>
       </c>
       <c r="C5" t="n">
-        <v>64920</v>
+        <v>65390</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+328</t>
+          <t>+265</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>64628</v>
+        <v>65161</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14165</v>
+        <v>14380</v>
       </c>
       <c r="C6" t="n">
-        <v>14165</v>
+        <v>14380</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+159</t>
+          <t>+100</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>14006</v>
+        <v>14280</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15397</v>
+        <v>15569</v>
       </c>
       <c r="C7" t="n">
-        <v>15397</v>
+        <v>15569</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+168</t>
+          <t>+63</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15229</v>
+        <v>15506</v>
       </c>
     </row>
     <row r="8">
@@ -578,16 +578,18 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -597,18 +599,18 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12382</v>
+        <v>12478</v>
       </c>
       <c r="C9" t="n">
-        <v>12248</v>
+        <v>12343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+23</t>
+          <t>+62</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>12359</v>
+        <v>12416</v>
       </c>
     </row>
     <row r="10">
@@ -618,10 +620,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>200096</v>
+        <v>202506</v>
       </c>
       <c r="C10" t="n">
-        <v>199885</v>
+        <v>202293</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -659,7 +661,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -710,7 +712,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -728,7 +730,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -746,7 +748,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -764,7 +766,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -782,7 +784,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -854,7 +856,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -868,11 +870,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>APR北京北苑龙湖</t>
+          <t>APR上海陆悦天地</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -890,7 +892,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -908,7 +910,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -926,7 +928,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -944,7 +946,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -962,7 +964,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -980,7 +982,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -998,7 +1000,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1016,7 +1018,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1034,7 +1036,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1052,7 +1054,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1088,7 +1090,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1106,7 +1108,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1124,7 +1126,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1142,7 +1144,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1160,7 +1162,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1214,7 +1216,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D30" t="n">
         <v>4</v>
@@ -1232,7 +1234,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>22012</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21974</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+142</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>21870</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21832</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+94</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>21776</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>27001</v>
+      </c>
+      <c r="C3" t="n">
+        <v>27000</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+310</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>26691</v>
-      </c>
-      <c r="C3" t="n">
-        <v>26690</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+301</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>26390</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>46398</v>
+      </c>
+      <c r="C4" t="n">
+        <v>46395</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+310</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>46088</v>
-      </c>
-      <c r="C4" t="n">
-        <v>46085</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+323</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>45765</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>65757</v>
+      </c>
+      <c r="C5" t="n">
+        <v>65721</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+331</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>65426</v>
-      </c>
-      <c r="C5" t="n">
-        <v>65390</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+265</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>65161</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>13495</v>
+      </c>
+      <c r="C6" t="n">
+        <v>13495</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-885</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>14380</v>
-      </c>
-      <c r="C6" t="n">
-        <v>14380</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+100</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>14280</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>15642</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15642</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+73</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>15569</v>
-      </c>
-      <c r="C7" t="n">
-        <v>15569</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+63</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>15506</v>
       </c>
     </row>
     <row r="8">
@@ -578,18 +578,18 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>1012</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1012</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+1008</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>4</v>
-      </c>
-      <c r="C8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -599,18 +599,18 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>12514</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12379</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+36</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>12478</v>
-      </c>
-      <c r="C9" t="n">
-        <v>12343</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+62</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>12416</v>
       </c>
     </row>
     <row r="10">
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>202506</v>
+        <v>203831</v>
       </c>
       <c r="C10" t="n">
-        <v>202293</v>
+        <v>203618</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -639,7 +639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,11 +657,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>（旧）APR成都天府环宇坊</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>（旧）APR成都环球中心</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>（旧）APR成都东安天街</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>（旧）APR成都凯德魅力城</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>DJI上海FFC滨江悅里授权体验店</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>4</v>
+      <c r="B6" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -712,7 +752,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -730,7 +770,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -748,7 +788,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -766,7 +806,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -784,7 +824,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -856,7 +896,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -892,7 +932,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -910,7 +950,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -928,7 +968,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -946,7 +986,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -964,7 +1004,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -982,7 +1022,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1000,7 +1040,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1018,7 +1058,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1036,7 +1076,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1054,7 +1094,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1090,7 +1130,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1104,11 +1144,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>APR成都凯德魅力城</t>
+          <t>APR成都天府大悦城</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1122,11 +1162,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>APR成都天府大悦城</t>
+          <t>APR成都双楠伊藤</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>151</v>
+        <v>224</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1140,11 +1180,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>APR成都双楠伊藤</t>
+          <t>APR成都武侯吾悦</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,14 +452,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22012</v>
+        <v>22042</v>
       </c>
       <c r="C2" t="n">
-        <v>21974</v>
+        <v>22004</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+142</t>
+          <t>+172</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -473,14 +473,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27001</v>
+        <v>27048</v>
       </c>
       <c r="C3" t="n">
-        <v>27000</v>
+        <v>27047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+310</t>
+          <t>+357</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -494,14 +494,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46398</v>
+        <v>46447</v>
       </c>
       <c r="C4" t="n">
-        <v>46395</v>
+        <v>46444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+310</t>
+          <t>+359</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -515,14 +515,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65757</v>
+        <v>65809</v>
       </c>
       <c r="C5" t="n">
-        <v>65721</v>
+        <v>65773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+331</t>
+          <t>+383</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -536,14 +536,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13495</v>
+        <v>13508</v>
       </c>
       <c r="C6" t="n">
-        <v>13495</v>
+        <v>13508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-885</t>
+          <t>-872</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -557,14 +557,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15642</v>
+        <v>15654</v>
       </c>
       <c r="C7" t="n">
-        <v>15642</v>
+        <v>15654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+73</t>
+          <t>+85</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -578,14 +578,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C8" t="n">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+1008</t>
+          <t>+1009</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -599,14 +599,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12514</v>
+        <v>12554</v>
       </c>
       <c r="C9" t="n">
-        <v>12379</v>
+        <v>12419</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+36</t>
+          <t>+76</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>203831</v>
+        <v>204075</v>
       </c>
       <c r="C10" t="n">
-        <v>203618</v>
+        <v>203862</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D30" t="n">
         <v>4</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,14 +452,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22042</v>
+        <v>22082</v>
       </c>
       <c r="C2" t="n">
-        <v>22004</v>
+        <v>22044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+172</t>
+          <t>+212</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -473,14 +473,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27048</v>
+        <v>21049</v>
       </c>
       <c r="C3" t="n">
-        <v>27047</v>
+        <v>21048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+357</t>
+          <t>-5642</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -494,14 +494,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46447</v>
+        <v>46535</v>
       </c>
       <c r="C4" t="n">
-        <v>46444</v>
+        <v>46532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+359</t>
+          <t>+447</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -515,14 +515,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65809</v>
+        <v>65885</v>
       </c>
       <c r="C5" t="n">
-        <v>65773</v>
+        <v>65849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+383</t>
+          <t>+459</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -536,14 +536,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13508</v>
+        <v>7342</v>
       </c>
       <c r="C6" t="n">
-        <v>13508</v>
+        <v>7342</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-872</t>
+          <t>-7038</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -557,14 +557,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15654</v>
+        <v>15673</v>
       </c>
       <c r="C7" t="n">
-        <v>15654</v>
+        <v>15673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+85</t>
+          <t>+104</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -574,57 +574,49 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>（未匹配门店）</t>
+          <t>未消费会员</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1013</v>
+        <v>12561</v>
       </c>
       <c r="C8" t="n">
-        <v>1013</v>
+        <v>12426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+1009</t>
+          <t>+83</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>12478</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>未消费会员</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12554</v>
+        <v>191127</v>
       </c>
       <c r="C9" t="n">
-        <v>12419</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+76</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>12478</v>
-      </c>
+        <v>190914</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>剔除-门店标记剔除（不计入）</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>204075</v>
-      </c>
-      <c r="C10" t="n">
-        <v>203862</v>
-      </c>
+        <v>13279</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
     </row>
@@ -639,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,56 +644,6 @@
         <is>
           <t>记录数</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>（旧）APR成都天府环宇坊</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>（旧）APR成都环球中心</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>（旧）APR成都东安天街</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>（旧）APR成都凯德魅力城</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DJI上海FFC滨江悅里授权体验店</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -748,11 +690,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DJI上海天荟广场授权体验店</t>
+          <t>DJI上海FFC滨江悅里授权体验店</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -766,11 +708,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+          <t>DJI上海天荟广场授权体验店</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>381</v>
+        <v>121</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -784,11 +726,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DJI上海百联南桥购物中心授权体验店</t>
+          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>426</v>
+        <v>381</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -802,11 +744,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DJI上海第一八佰伴授权体验店</t>
+          <t>DJI上海百联南桥购物中心授权体验店</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -820,11 +762,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DJI上海维璟印象城授权体验店</t>
+          <t>DJI上海第一八佰伴授权体验店</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>522</v>
+        <v>446</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -838,11 +780,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>APR上海唐镇印象汇</t>
+          <t>华为北京常营龙湖</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -856,11 +798,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>APR上海三林印象汇</t>
+          <t>APR北京昌发展万科</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -874,11 +816,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>华为北京常营龙湖</t>
+          <t>APR北京北苑龙湖</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>111</v>
+        <v>225</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -892,11 +834,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>APR北京昌发展万科</t>
+          <t>APR北京槐房万达</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -910,11 +852,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>APR上海陆悦天地</t>
+          <t>APR北京大红门银泰</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -932,7 +874,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -950,7 +892,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -986,7 +928,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -1004,7 +946,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -1022,7 +964,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1040,7 +982,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1058,7 +1000,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1076,7 +1018,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1094,7 +1036,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1108,11 +1050,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>APR昆明万象城</t>
+          <t>APR成都武侯大悦城</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1126,11 +1068,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>APR成都武侯大悦城</t>
+          <t>（旧）APR成都凯德魅力城</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1166,7 +1108,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1184,7 +1126,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>22187</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22149</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+105</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>22082</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22044</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+212</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>21870</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>21254</v>
+      </c>
+      <c r="C3" t="n">
+        <v>21253</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+205</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>21049</v>
-      </c>
-      <c r="C3" t="n">
-        <v>21048</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>-5642</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>26691</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>46708</v>
+      </c>
+      <c r="C4" t="n">
+        <v>46705</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+173</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>46535</v>
-      </c>
-      <c r="C4" t="n">
-        <v>46532</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+447</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>46088</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>66078</v>
+      </c>
+      <c r="C5" t="n">
+        <v>66042</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+193</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>65885</v>
-      </c>
-      <c r="C5" t="n">
-        <v>65849</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+459</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>65426</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>7425</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7425</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+83</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>7342</v>
-      </c>
-      <c r="C6" t="n">
-        <v>7342</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>-7038</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>14380</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>15738</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15738</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+65</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>15673</v>
-      </c>
-      <c r="C7" t="n">
-        <v>15673</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+104</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>15569</v>
       </c>
     </row>
     <row r="8">
@@ -578,18 +578,18 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>12547</v>
+      </c>
+      <c r="C8" t="n">
+        <v>12412</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-14</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>12561</v>
-      </c>
-      <c r="C8" t="n">
-        <v>12426</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+83</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>12478</v>
       </c>
     </row>
     <row r="9">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>191127</v>
+        <v>191937</v>
       </c>
       <c r="C9" t="n">
-        <v>190914</v>
+        <v>191724</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1050,11 +1050,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>APR成都武侯大悦城</t>
+          <t>APR成都凯德魅力城</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1068,11 +1068,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>（旧）APR成都凯德魅力城</t>
+          <t>APR成都东安天街</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>133</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1086,11 +1086,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>APR成都天府大悦城</t>
+          <t>APR成都环球中心</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>159</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1104,11 +1104,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>APR成都双楠伊藤</t>
+          <t>APR成都天府环宇坊</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>227</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1122,11 +1122,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>APR成都武侯吾悦</t>
+          <t>APR成都武侯大悦城</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>230</v>
+        <v>133</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,14 +452,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22845</v>
+        <v>22867</v>
       </c>
       <c r="C2" t="n">
-        <v>22807</v>
+        <v>22829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+100</t>
+          <t>+122</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -473,14 +473,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23060</v>
+        <v>23090</v>
       </c>
       <c r="C3" t="n">
-        <v>23059</v>
+        <v>23089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+255</t>
+          <t>+285</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -494,14 +494,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48715</v>
+        <v>48773</v>
       </c>
       <c r="C4" t="n">
-        <v>48711</v>
+        <v>48769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+330</t>
+          <t>+388</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -515,14 +515,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68332</v>
+        <v>68364</v>
       </c>
       <c r="C5" t="n">
-        <v>68296</v>
+        <v>68328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+284</t>
+          <t>+316</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -536,14 +536,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8276</v>
+        <v>8301</v>
       </c>
       <c r="C6" t="n">
-        <v>8276</v>
+        <v>8301</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+141</t>
+          <t>+166</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -557,14 +557,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16279</v>
+        <v>16291</v>
       </c>
       <c r="C7" t="n">
-        <v>16279</v>
+        <v>16291</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+91</t>
+          <t>+103</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -578,14 +578,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12806</v>
+        <v>12851</v>
       </c>
       <c r="C8" t="n">
-        <v>12661</v>
+        <v>12705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+68</t>
+          <t>+113</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>200313</v>
+        <v>200537</v>
       </c>
       <c r="C9" t="n">
-        <v>200089</v>
+        <v>200312</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>23027</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22989</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+160</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>22867</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22829</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+122</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>22745</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>23492</v>
+      </c>
+      <c r="C3" t="n">
+        <v>23491</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+402</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>23090</v>
-      </c>
-      <c r="C3" t="n">
-        <v>23089</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+285</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>22805</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>49290</v>
+      </c>
+      <c r="C4" t="n">
+        <v>49286</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+517</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>48773</v>
-      </c>
-      <c r="C4" t="n">
-        <v>48769</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+388</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>48385</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>68750</v>
+      </c>
+      <c r="C5" t="n">
+        <v>68714</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+386</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>68364</v>
-      </c>
-      <c r="C5" t="n">
-        <v>68328</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+316</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>68048</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>8514</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8514</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+213</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>8301</v>
-      </c>
-      <c r="C6" t="n">
-        <v>8301</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+166</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>8135</v>
       </c>
     </row>
     <row r="7">
@@ -557,68 +557,87 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>16430</v>
+      </c>
+      <c r="C7" t="n">
+        <v>16430</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+139</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>16291</v>
-      </c>
-      <c r="C7" t="n">
-        <v>16291</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+103</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>16188</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>未消费会员</t>
+          <t>（未匹配门店）</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12851</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>12705</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+113</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>12738</v>
-      </c>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>未消费会员</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>200537</v>
+        <v>13011</v>
       </c>
       <c r="C9" t="n">
-        <v>200312</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+        <v>12862</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+160</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>12851</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>剔除-门店标记剔除（不计入）</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13279</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>202516</v>
+      </c>
+      <c r="C10" t="n">
+        <v>202288</v>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>剔除-门店标记剔除（不计入）</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>13279</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -631,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,6 +663,16 @@
         <is>
           <t>记录数</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DJI北京双安商场授权体验店</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -694,7 +723,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -712,7 +741,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -730,7 +759,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -748,7 +777,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -766,7 +795,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -802,7 +831,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -820,7 +849,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -838,7 +867,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -856,7 +885,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -874,7 +903,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -892,7 +921,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -910,7 +939,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -928,7 +957,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -946,7 +975,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -964,7 +993,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -982,7 +1011,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1000,7 +1029,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1018,7 +1047,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1036,7 +1065,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1050,11 +1079,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>APR成都凯德魅力城</t>
+          <t>APR成都东安天街</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1068,11 +1097,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>APR成都东安天街</t>
+          <t>APR成都凯德魅力城</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1090,7 +1119,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1108,7 +1137,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1144,7 +1173,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1198,7 +1227,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D30" t="n">
         <v>4</v>
@@ -1216,7 +1245,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>23113</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23075</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+86</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>23027</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22989</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+160</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>22867</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>23634</v>
+      </c>
+      <c r="C3" t="n">
+        <v>23633</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+142</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>23492</v>
-      </c>
-      <c r="C3" t="n">
-        <v>23491</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+402</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>23090</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>49452</v>
+      </c>
+      <c r="C4" t="n">
+        <v>49448</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+162</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>49290</v>
-      </c>
-      <c r="C4" t="n">
-        <v>49286</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+517</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>48773</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>68902</v>
+      </c>
+      <c r="C5" t="n">
+        <v>68866</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+152</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>68750</v>
-      </c>
-      <c r="C5" t="n">
-        <v>68714</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+386</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>68364</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>8579</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8579</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+65</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>8514</v>
-      </c>
-      <c r="C6" t="n">
-        <v>8514</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+213</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>8301</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>16495</v>
+      </c>
+      <c r="C7" t="n">
+        <v>16495</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+65</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>16430</v>
-      </c>
-      <c r="C7" t="n">
-        <v>16430</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+139</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>16291</v>
       </c>
     </row>
     <row r="8">
@@ -578,17 +578,19 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -597,18 +599,18 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>12989</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12839</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-22</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>13011</v>
-      </c>
-      <c r="C9" t="n">
-        <v>12862</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+160</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>12851</v>
       </c>
     </row>
     <row r="10">
@@ -618,10 +620,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>202516</v>
+        <v>203170</v>
       </c>
       <c r="C10" t="n">
-        <v>202288</v>
+        <v>202941</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -672,7 +674,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +725,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -741,7 +743,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -759,7 +761,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -777,7 +779,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -795,7 +797,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -831,7 +833,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -849,7 +851,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -867,7 +869,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -885,7 +887,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -903,7 +905,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -939,7 +941,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -957,7 +959,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -975,7 +977,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -993,7 +995,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1011,7 +1013,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1029,7 +1031,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1047,7 +1049,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1065,7 +1067,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1083,7 +1085,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1101,7 +1103,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1119,7 +1121,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1137,7 +1139,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1173,7 +1175,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1227,7 +1229,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D30" t="n">
         <v>4</v>
@@ -1245,7 +1247,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>23270</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23232</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+157</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>23113</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23075</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+86</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>23027</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>23980</v>
+      </c>
+      <c r="C3" t="n">
+        <v>23979</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+346</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>23634</v>
-      </c>
-      <c r="C3" t="n">
-        <v>23633</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+142</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>23492</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>49980</v>
+      </c>
+      <c r="C4" t="n">
+        <v>49976</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+528</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>49452</v>
-      </c>
-      <c r="C4" t="n">
-        <v>49448</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+162</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>49290</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>69334</v>
+      </c>
+      <c r="C5" t="n">
+        <v>69298</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+432</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>68902</v>
-      </c>
-      <c r="C5" t="n">
-        <v>68866</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+152</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>68750</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>8737</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8737</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+158</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>8579</v>
-      </c>
-      <c r="C6" t="n">
-        <v>8579</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+65</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>8514</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>16634</v>
+      </c>
+      <c r="C7" t="n">
+        <v>16634</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+139</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>16495</v>
-      </c>
-      <c r="C7" t="n">
-        <v>16495</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+65</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>16430</v>
       </c>
     </row>
     <row r="8">
@@ -578,18 +578,18 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>14</v>
+      </c>
+      <c r="C8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+8</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>6</v>
-      </c>
-      <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -599,18 +599,18 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>13020</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12871</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+31</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>12989</v>
-      </c>
-      <c r="C9" t="n">
-        <v>12839</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>-22</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>13011</v>
       </c>
     </row>
     <row r="10">
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>203170</v>
+        <v>204969</v>
       </c>
       <c r="C10" t="n">
-        <v>202941</v>
+        <v>204741</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DJI北京龙湖熙悦天街授权体验店</t>
+          <t>DJI北京万柳华联授权体验店</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1045,11 +1045,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DJI北京万柳华联授权体验店</t>
+          <t>DJI北京龙湖熙悦天街授权体验店</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1081,11 +1081,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>APR成都东安天街</t>
+          <t>APR成都凯德魅力城</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>APR成都凯德魅力城</t>
+          <t>APR成都东安天街</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>23520</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23482</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+250</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>23270</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23232</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+157</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>23113</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>24424</v>
+      </c>
+      <c r="C3" t="n">
+        <v>24423</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+444</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>23980</v>
-      </c>
-      <c r="C3" t="n">
-        <v>23979</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+346</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>23634</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>50652</v>
+      </c>
+      <c r="C4" t="n">
+        <v>50648</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+672</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>49980</v>
-      </c>
-      <c r="C4" t="n">
-        <v>49976</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+528</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>49452</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>69875</v>
+      </c>
+      <c r="C5" t="n">
+        <v>69839</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+541</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>69334</v>
-      </c>
-      <c r="C5" t="n">
-        <v>69298</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+432</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>68902</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>8961</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8961</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+224</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>8737</v>
-      </c>
-      <c r="C6" t="n">
-        <v>8737</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+158</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>8579</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>16800</v>
+      </c>
+      <c r="C7" t="n">
+        <v>16800</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+166</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>16634</v>
-      </c>
-      <c r="C7" t="n">
-        <v>16634</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+139</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>16495</v>
       </c>
     </row>
     <row r="8">
@@ -578,18 +578,18 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>27</v>
+      </c>
+      <c r="C8" t="n">
+        <v>27</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+13</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>14</v>
-      </c>
-      <c r="C8" t="n">
-        <v>14</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+8</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -599,18 +599,18 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>13075</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12926</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+55</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>13020</v>
-      </c>
-      <c r="C9" t="n">
-        <v>12871</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+31</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>12989</v>
       </c>
     </row>
     <row r="10">
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>204969</v>
+        <v>207334</v>
       </c>
       <c r="C10" t="n">
-        <v>204741</v>
+        <v>207106</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,7 +674,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DJI上海徐汇万科广场授权体验店</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -725,7 +735,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -743,7 +753,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -761,7 +771,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -779,7 +789,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -797,7 +807,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -833,7 +843,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -851,7 +861,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -869,7 +879,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -887,7 +897,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -905,7 +915,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -923,7 +933,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -941,7 +951,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -959,7 +969,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -977,7 +987,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -995,7 +1005,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1013,7 +1023,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1031,7 +1041,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1049,7 +1059,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1067,7 +1077,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1085,7 +1095,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1103,7 +1113,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1121,7 +1131,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1139,7 +1149,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1175,7 +1185,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1247,7 +1257,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>23736</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23698</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+216</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>23520</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23482</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+250</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>23270</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>24855</v>
+      </c>
+      <c r="C3" t="n">
+        <v>24854</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+431</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>24424</v>
-      </c>
-      <c r="C3" t="n">
-        <v>24423</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+444</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>23980</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>51281</v>
+      </c>
+      <c r="C4" t="n">
+        <v>51277</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+629</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>50652</v>
-      </c>
-      <c r="C4" t="n">
-        <v>50648</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+672</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>49980</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>70369</v>
+      </c>
+      <c r="C5" t="n">
+        <v>70333</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+494</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>69875</v>
-      </c>
-      <c r="C5" t="n">
-        <v>69839</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+541</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>69334</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>9202</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9202</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+241</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>8961</v>
-      </c>
-      <c r="C6" t="n">
-        <v>8961</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+224</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>8737</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>16973</v>
+      </c>
+      <c r="C7" t="n">
+        <v>16973</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+173</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>16800</v>
-      </c>
-      <c r="C7" t="n">
-        <v>16800</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+166</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>16634</v>
       </c>
     </row>
     <row r="8">
@@ -578,18 +578,18 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>34</v>
+      </c>
+      <c r="C8" t="n">
+        <v>34</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+7</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>27</v>
-      </c>
-      <c r="C8" t="n">
-        <v>27</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+13</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -599,18 +599,18 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>13114</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12964</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+39</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>13075</v>
-      </c>
-      <c r="C9" t="n">
-        <v>12926</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+55</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>13020</v>
       </c>
     </row>
     <row r="10">
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>207334</v>
+        <v>209564</v>
       </c>
       <c r="C10" t="n">
-        <v>207106</v>
+        <v>209335</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -983,11 +983,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>华为北京丰台鑫嘉汇</t>
+          <t>华为北京房山燕隆汇</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,14 +452,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23736</v>
+        <v>23746</v>
       </c>
       <c r="C2" t="n">
-        <v>23698</v>
+        <v>23708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+216</t>
+          <t>+226</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -515,14 +515,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70369</v>
+        <v>70393</v>
       </c>
       <c r="C5" t="n">
-        <v>70333</v>
+        <v>70357</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+494</t>
+          <t>+518</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -574,72 +574,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>（未匹配门店）</t>
+          <t>未消费会员</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34</v>
+        <v>13114</v>
       </c>
       <c r="C8" t="n">
-        <v>34</v>
+        <v>12964</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+39</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>13075</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>未消费会员</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13114</v>
+        <v>209564</v>
       </c>
       <c r="C9" t="n">
-        <v>12964</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+39</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>13075</v>
-      </c>
+        <v>209335</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>剔除-门店标记剔除（不计入）</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>209564</v>
-      </c>
-      <c r="C10" t="n">
-        <v>209335</v>
-      </c>
+        <v>13279</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>剔除-门店标记剔除（不计入）</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>13279</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -652,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -665,26 +644,6 @@
         <is>
           <t>记录数</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DJI北京双安商场授权体验店</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DJI上海徐汇万科广场授权体验店</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -731,11 +690,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DJI上海FFC滨江悅里授权体验店</t>
+          <t>DJI上海徐汇万科广场授权体验店</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -749,11 +708,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海FFC滨江悅里授权体验店</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -767,11 +726,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DJI上海天荟广场授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>167</v>
+        <v>57</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -785,11 +744,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+          <t>DJI上海天荟广场授权体验店</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>452</v>
+        <v>167</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -803,11 +762,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DJI上海百联南桥购物中心授权体验店</t>
+          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>481</v>
+        <v>452</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -1001,11 +960,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DJI北京北投新奥天虹授权体验店</t>
+          <t>DJI北京双安商场授权体验店</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>267</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1019,11 +978,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DJI北京龙湖长安天街授权体验店</t>
+          <t>DJI北京北投新奥天虹授权体验店</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>344</v>
+        <v>267</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1037,11 +996,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DJI北京万柳华联授权体验店</t>
+          <t>DJI北京龙湖长安天街授权体验店</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>404</v>
+        <v>344</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1055,11 +1014,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DJI北京龙湖熙悦天街授权体验店</t>
+          <t>DJI北京万柳华联授权体验店</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1073,11 +1032,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DJI北京首都机场授权体验店</t>
+          <t>DJI北京龙湖熙悦天街授权体验店</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>526</v>
+        <v>428</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,14 +452,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23885</v>
+        <v>24094</v>
       </c>
       <c r="C2" t="n">
-        <v>23847</v>
+        <v>24056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+139</t>
+          <t>+348</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -473,14 +473,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25157</v>
+        <v>25531</v>
       </c>
       <c r="C3" t="n">
-        <v>25156</v>
+        <v>25530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+302</t>
+          <t>+676</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -494,14 +494,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>51684</v>
+        <v>52074</v>
       </c>
       <c r="C4" t="n">
-        <v>51680</v>
+        <v>52070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+403</t>
+          <t>+793</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -515,14 +515,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70728</v>
+        <v>71144</v>
       </c>
       <c r="C5" t="n">
-        <v>70692</v>
+        <v>71107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+335</t>
+          <t>+751</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -536,14 +536,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9326</v>
+        <v>9510</v>
       </c>
       <c r="C6" t="n">
-        <v>9326</v>
+        <v>9510</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+124</t>
+          <t>+308</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -557,14 +557,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17091</v>
+        <v>17210</v>
       </c>
       <c r="C7" t="n">
-        <v>17091</v>
+        <v>17210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+118</t>
+          <t>+237</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -578,14 +578,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13135</v>
+        <v>13175</v>
       </c>
       <c r="C8" t="n">
-        <v>12984</v>
+        <v>13024</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+21</t>
+          <t>+61</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>211006</v>
+        <v>212738</v>
       </c>
       <c r="C9" t="n">
-        <v>210776</v>
+        <v>212507</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,13 +452,15 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24094</v>
+        <v>24386</v>
       </c>
       <c r="C2" t="n">
-        <v>24056</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+        <v>24348</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+292</t>
+        </is>
       </c>
       <c r="E2" t="n">
         <v>24094</v>
@@ -471,13 +473,15 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25531</v>
+        <v>26014</v>
       </c>
       <c r="C3" t="n">
-        <v>25530</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
+        <v>26013</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+483</t>
+        </is>
       </c>
       <c r="E3" t="n">
         <v>25531</v>
@@ -490,13 +494,15 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52074</v>
+        <v>52577</v>
       </c>
       <c r="C4" t="n">
-        <v>52070</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
+        <v>52573</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+503</t>
+        </is>
       </c>
       <c r="E4" t="n">
         <v>52074</v>
@@ -509,14 +515,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71145</v>
+        <v>71598</v>
       </c>
       <c r="C5" t="n">
-        <v>71108</v>
+        <v>71561</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+454</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -530,13 +536,15 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9510</v>
+        <v>9768</v>
       </c>
       <c r="C6" t="n">
-        <v>9510</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
+        <v>9768</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+258</t>
+        </is>
       </c>
       <c r="E6" t="n">
         <v>9510</v>
@@ -549,13 +557,15 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17210</v>
+        <v>17368</v>
       </c>
       <c r="C7" t="n">
-        <v>17210</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
+        <v>17368</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+158</t>
+        </is>
       </c>
       <c r="E7" t="n">
         <v>17210</v>
@@ -568,14 +578,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13174</v>
+        <v>13214</v>
       </c>
       <c r="C8" t="n">
-        <v>13023</v>
+        <v>13063</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>+39</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -589,10 +599,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>212738</v>
+        <v>214925</v>
       </c>
       <c r="C9" t="n">
-        <v>212507</v>
+        <v>214694</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -684,7 +694,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -702,7 +712,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -720,7 +730,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -738,7 +748,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -756,7 +766,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -792,7 +802,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -810,7 +820,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -828,7 +838,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -846,7 +856,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -864,7 +874,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -882,7 +892,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -900,7 +910,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -918,7 +928,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -936,7 +946,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -954,7 +964,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -972,7 +982,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -990,7 +1000,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1008,7 +1018,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1026,7 +1036,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1044,7 +1054,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1062,7 +1072,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1080,7 +1090,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1098,7 +1108,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1134,7 +1144,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1188,7 +1198,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D30" t="n">
         <v>4</v>
@@ -1206,7 +1216,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,163 +448,112 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25426</v>
+        <v>566</v>
       </c>
       <c r="C2" t="n">
-        <v>25426</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+        <v>566</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-54429</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>25426</v>
+        <v>54995</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27959</v>
+        <v>158</v>
       </c>
       <c r="C3" t="n">
-        <v>27958</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
+        <v>158</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-17890</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>27959</v>
+        <v>18048</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>（未匹配门店）</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54995</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
-        <v>54991</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>54995</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+26</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>未消费会员</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74109</v>
+        <v>45</v>
       </c>
       <c r="C5" t="n">
-        <v>74108</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-11845</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>74109</v>
+        <v>11890</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10809</v>
+        <v>795</v>
       </c>
       <c r="C6" t="n">
-        <v>10809</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>10809</v>
-      </c>
+        <v>795</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>剔除-门店标记剔除（不计入）</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18048</v>
-      </c>
-      <c r="C7" t="n">
-        <v>18048</v>
-      </c>
-      <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>18048</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>未消费会员</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>11890</v>
-      </c>
-      <c r="C8" t="n">
-        <v>11811</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>11890</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>223236</v>
-      </c>
-      <c r="C9" t="n">
-        <v>223151</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>剔除-门店标记剔除（不计入）</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>13265</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -617,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -630,6 +579,36 @@
         <is>
           <t>记录数</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>华为宁德霞浦方圆荟</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>华为宁德古田中央名城</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>华为宁德霞浦太康路二店</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,16 +650,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DJI上海徐汇万科广场授权体验店</t>
+          <t>华为北京丰台鑫嘉汇</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -689,16 +668,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DJI上海FFC滨江悅里授权体验店</t>
+          <t>华为北京同成街华联</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -707,16 +686,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>华为北京上德银泰</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -725,16 +704,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DJI上海天荟广场授权体验店</t>
+          <t>华为北京回龙观一店</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>208</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -743,16 +722,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+          <t>华为北京房山燕隆汇</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>516</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -761,16 +740,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>华为北京常营龙湖</t>
+          <t>华为厦门思明大西洋天虹</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -779,16 +758,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>APR北京昌发展万科</t>
+          <t>华为福州宜家荟聚</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>268</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -797,16 +776,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APR北京北苑龙湖</t>
+          <t>华为厦门思明加州广场</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>291</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -815,16 +794,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>APR北京大红门银泰</t>
+          <t>华为福州仓山爱琴海</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>319</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -833,378 +812,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>APR北京大峡谷凯德茂</t>
+          <t>华为福州砂之船奥莱</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>344</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>北京易联</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>华为北京回龙观一店</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>292</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>北京易联</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>华为北京京投小站</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>330</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>北京易联</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>华为北京上德银泰</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>418</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>北京易联</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>华为北京同成街华联</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>443</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>北京易联</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>华为北京房山燕隆汇</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>501</v>
-      </c>
-      <c r="D16" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>北京飞航</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>DJI北京双安商场授权体验店</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>71</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>北京飞航</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>DJI北京北投新奥天虹授权体验店</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>343</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>北京飞航</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>DJI北京龙湖长安天街授权体验店</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>407</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>北京飞航</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>DJI北京万柳华联授权体验店</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>451</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>北京飞航</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>DJI北京龙湖熙悦天街授权体验店</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>522</v>
-      </c>
-      <c r="D21" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>四川新跃</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>APR成都凯德魅力城</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>99</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>四川新跃</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>APR成都东安天街</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>110</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>四川新跃</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>APR成都天府环宇坊</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>121</v>
-      </c>
-      <c r="D24" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>四川新跃</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>（旧）APR成都凯德魅力城</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>133</v>
-      </c>
-      <c r="D25" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>四川新跃</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>APR成都环球中心</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>156</v>
-      </c>
-      <c r="D26" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>福建易联</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>华为厦门思明星河COCO Park</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>40</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>福建易联</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>华为厦门湖里江头</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>144</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>福建易联</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>华为福州福清高山</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>145</v>
-      </c>
-      <c r="D29" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>福建易联</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>华为厦门思明大西洋天虹</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>181</v>
-      </c>
-      <c r="D30" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>福建易联</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>华为厦门思明君尚天虹</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>225</v>
-      </c>
-      <c r="D31" t="n">
         <v>5</v>
       </c>
     </row>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -511,14 +511,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19738</v>
+        <v>19739</v>
       </c>
       <c r="C5" t="n">
-        <v>19738</v>
+        <v>19739</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+19580</t>
+          <t>+19581</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>87400</v>
+        <v>87401</v>
       </c>
       <c r="C8" t="n">
-        <v>87368</v>
+        <v>87369</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
